--- a/hpi_scraper/NewsAnnouncements/google_news_rss/google_news_rss_data.xlsx
+++ b/hpi_scraper/NewsAnnouncements/google_news_rss/google_news_rss_data.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
@@ -518,42 +518,42 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Singtel taps Siddharth Sharma for senior leadership role - Communications Today</t>
+          <t>Sea Limited: Brazil’s Success Opens A New Chapter Of Growth (NYSE:SE) - Seeking Alpha</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Singtel taps Siddharth Sharma for senior leadership role - Communications Today</t>
+          <t>Sea Limited: Brazil’s Success Opens A New Chapter Of Growth (NYSE:SE) - Seeking Alpha</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOczZPMFE4Rk9veDJTY3RIMVpiRGlBTXhaXzNudl81NGtsQ21XUm1nVmxLZVJrTXNPMDVieThnZndHMUxkWkpGQ01wTmVmVVNHVUFMMmZyYU9MUUdDVWpnVV9UNG5oNmJrbExzTHFEdnFZcXIydGg0NjlEdDRiRjFHcWpsZHo1S2lUcjMzZHJXcF8zRmZnaEJ6Nk1ESQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQX05YMGI4ZUEzeGZHWnVnNTVua0M5ZnVoLUlEUm9XRDFPYzNXUzBuQ3dvY21aU3I0emUxS2stUHh6MzZ0X2k3b2trQ0w4RUVaOWFmUC1UWW8wVVJPZUpOR0Q4RDVWNDE5a01hTW5sMUJWdFczNmt4RnpMUzR2VUo5azdBQTk1MDdhRXRELUNXeUxxV0hJM0c4Y09sRF91N29uSWIwV1o5WQ?oc=5</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -575,42 +575,42 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Shares of Singapore Telecommunications open up 1.9% after STT GDC acquisition announcement - marketscreener.com</t>
+          <t>Sea Limited (SE) Enters a Strategic Partnership with Google, Here’s What You Need to Know - Yahoo Finance</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Shares of Singapore Telecommunications open up 1.9% after STT GDC acquisition announcement - marketscreener.com</t>
+          <t>Sea Limited (SE) Enters a Strategic Partnership with Google, Here’s What You Need to Know - Yahoo Finance</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNTS1iNUhpSXBlb2RvNHRBWTlMNUxnS1VwTldJeGEzS1FYQ1lNVE5hRnNXcm1oamlvYUVpT1dJNFNNZmtFS1plRjdLc0Z5X3NYZHVZUUJDaEsxVjdUMWhfWTZfdjJyMGV0TW53bENlalVqODdDQ2VQU2JGN19pbjZVYXljMVMyZ0Ztbm5xcEZvTWxxZTV4Qm1hTk01TFlYSmVLR1FzRWY4TTg2ODRLajVQZ1d5TTVsT0FQcl9LbEdJdE9CeE5FVkhEOHZrYXVnWFZ1a0lqM3B3Z3NzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPdlhzbFphNEdNY1BPbkExZlBWYkVSNDNwTjY0cFR6RENhRHpHbnZYRHE1TThlNy0wRUNOSXc3cTV0amFXTDlZN191bUswQjl2YU53TWxsZTNoM1R6VFMxV1c2STRhYUVSMmhZcVlmblFBTzdOVW40VkNnMHFrWUdSS0h3NA?oc=5</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -632,37 +632,37 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications Ltd wins two awards at Retail Asia Awards 2026 - Retail Asia</t>
+          <t>Sea Limited Gears Up to Report Q1 Earnings: What's in the Offing? - TradingView</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications Ltd wins two awards at Retail Asia Awards 2026 - Retail Asia</t>
+          <t>Sea Limited Gears Up to Report Q1 Earnings: What's in the Offing? - TradingView</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSmk1SHhocnpmOFBaNE5nTmlDT1oyVFRUMVlUOHBJcm1lejkyU0Vod2lQcGdrUzN3S1gwRVJYOVNPVFZTaURrTTBpeTBnLWJLNEJnRXZZb0RYR1l1MEhrNFZROWxfLWJzR2sxS2Z1RFRaTUIxdDJEUXBISUI5V2N5RnkzYi1oSlY5bHhMdm5jckZ6aGE3cWZmcWl3REdScWFWQmNycDhEcTRlYmhkTmVvTW9EMnlnZDNUT0NNU3RRVEJoSHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPWjlQR3dWRlJsT3dVcHVSSGF0UUloS2FrWkNjZzcyUURoV0Vicll0TWdfLVQ0RzBCOG1OZUVFbWlqazRERWQ1T2FWbGxBYjRGOWQwSzBaSGk5NW9PT1ZLZmVQYy1yRmc5MV9ocWJITmtDWUJtd1lsaUJuYU1JTWpiUTBELVI1bnBNM2UtZDQ2Y2lvVE03REtfQU52SWQ1dXlsMFhYajJTRno4bmNvckhvZ0I0MlZCSnBDcEhN?oc=5</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -689,37 +689,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>KKR, Singtel seek to fully own Singapore data centre firm in $3.9 billion deal, sources say - Reuters</t>
+          <t>Why Did Sea Limited's Stock Plunge Despite Strong Revenue Growth - Kavout</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>KKR, Singtel seek to fully own Singapore data centre firm in $3.9 billion deal, sources say - Reuters</t>
+          <t>Why Did Sea Limited's Stock Plunge Despite Strong Revenue Growth - Kavout</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMlNiV0U4enVtOG82cjR6eXlxcDdVQXJkZ0NScU8wa1A4WFZ0MUE2dmN6MHVxUWQzMFZuX1hZMEpJc3g3Zk1TOU5IZklFc0xQOXcxcmFMZ0VHMUFfTkxNNjB6VUF6MTV0YTJkX3MyZjB6MGY2N3dkbTlOUHB4WmlkNVNMbURRcVJiNk4ySklXQ3h4MXIwOGJ4aGlnSTdGMFNVem5fMmlXSHRmS0tvMTVyS1hlYUhCbk5KTXJEbENNOU9fZ211MHZaXzRmbDJCYUhWVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPU0FoaVhTbjNvNG1vc3ZVU1JDUEx2VUtOenJ3ZDhJOTlWckc5UmlhX3BXNGFHV3pQN0p1bGk4MEhWN21qSXJMYlhsTGlOZ3E3bU9BMTBLV3ZwOHF6b0lVZzd0SlJzQm1tVFh5NG53eFZDU245aXBXcEJHeVpYVHU1Mm05NzFxNGRTTHhIM3hzdm5zeDhPZ09wNVVjczVXR2xl?oc=5</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -746,42 +746,42 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/singtel</t>
+          <t>https://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>KKR Seals $5.1B Data Center Mega-Deal as AI Demand Soars - The Tech Buzz</t>
+          <t>Sea Limited Q1 2026 Earnings: Revenue Surges 47% to $7 Billion - IndexBox</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>KKR Seals $5.1B Data Center Mega-Deal as AI Demand Soars - The Tech Buzz</t>
+          <t>Sea Limited Q1 2026 Earnings: Revenue Surges 47% to $7 Billion - IndexBox</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQOUNVNVBLVEtiVDFxbnlRSzROYVd1em5nMXdHMVZ6RDQzMU9JQ2p0SzVSS3ktZUdKZmZjcXJqLTdhak92UEV4WkF2c2lIc3pIOFVMS0ZqSE5Qb19iYU1xOW1ja2ZXVFd4a1Zra1dkbjdMMktlTHp0Z240cDUwd2NFWkRaUTFPTF9WUVB2M2E4SWhwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQVnQ4SENqT0hzazRPazZQUGU0NzU3SDJpM1NjUWdtWUpRdm9fazQzb09hSTB6RFd1YmVlTldlbEJhZVd4NTBZQWxVNzNFT0czRkV0ZlQ3TXg4WUdlS1RQTDI1ZXl6enQ5T1RaZW0tclhYeE8tdnJ2a3liRV9oMC1DQXhqVGlpV1BhMGZmYk5UaGpCZHc?oc=5</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
